--- a/Web/incidents_2000.xlsx
+++ b/Web/incidents_2000.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ростелеком\На хакатон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\ThreatPredictionSystemMIPT\Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFC6C84-E706-4DB8-9FDE-F4B73C275D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB74DCC-5A59-4166-A0B5-774E479F5800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10008" uniqueCount="4855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10007" uniqueCount="4854">
   <si>
     <t>Тип предприятия</t>
   </si>
@@ -14582,9 +14582,6 @@
   </si>
   <si>
     <t>6583</t>
-  </si>
-  <si>
-    <t>31.10.2023 00:48</t>
   </si>
 </sst>
 </file>
@@ -14640,11 +14637,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -14947,7 +14945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2001"/>
+  <dimension ref="A1:H2002"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.140625" bestFit="1" customWidth="1"/>
@@ -66982,8 +66980,13 @@
       <c r="G2001" t="s">
         <v>3281</v>
       </c>
-      <c r="H2001" t="s">
-        <v>4854</v>
+      <c r="H2001" s="2">
+        <v>45230.033333333333</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H2002" s="2">
+        <v>46118.033333333333</v>
       </c>
     </row>
   </sheetData>
